--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97715</v>
+        <v>97717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97717</v>
+        <v>97727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97727</v>
+        <v>97731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97731</v>
+        <v>97734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97734</v>
+        <v>97735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97735</v>
+        <v>97752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97768</v>
+        <v>97770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97770</v>
+        <v>97857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52299-2025 artfynd.xlsx
+++ b/artfynd/A 52299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851701</v>
       </c>
       <c r="B2" t="n">
-        <v>97857</v>
+        <v>97770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
